--- a/mosip_master/xlsx/zone.xlsx
+++ b/mosip_master/xlsx/zone.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Downloads\Sao-Tome-mosip-master\xlsx\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\eclipse-workspace\mosip-data\mosip_master\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B129A221-2894-49AF-9129-ECF8B3445820}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD5E9A57-2B76-46F3-83E8-BD21A19F4954}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="16">
   <si>
     <t>lang_code</t>
   </si>
@@ -67,6 +67,15 @@
   </si>
   <si>
     <t>São Tomé e Príncipe</t>
+  </si>
+  <si>
+    <t>eng</t>
+  </si>
+  <si>
+    <t>São Tomé and Príncipe</t>
+  </si>
+  <si>
+    <t>Country</t>
   </si>
 </sst>
 </file>
@@ -469,7 +478,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr defaultColWidth="8.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="3" width="17.90625" bestFit="1" customWidth="1"/>
@@ -529,6 +538,29 @@
         <v>8</v>
       </c>
     </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555496" footer="0.51180555555555496"/>
